--- a/www/ig/fhir/core/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-organization-uac.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="380">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,8 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This profile specializes the fr-core-organization profile to represent administrative units inside healthcare institutions.
-Ce profil spécialise le profil fr-core-organization pour représenter les unités administratives et comptables (UAC) en établissement</t>
+    <t>Ce profil permet de représenter les unités d'activité (UAC, parfois appelé PAC). L'UAC (Unité d'Activité) est le niveau élémentaire de recueil des activités en vue de la facturation.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -115,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Organization</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -424,7 +423,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -437,14 +436,14 @@
     <t>Organization.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -488,7 +487,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -512,7 +511,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -555,7 +554,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -631,11 +630,14 @@
     <t>shortName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Organization Short Name Extension</t>
+  </si>
+  <si>
+    <t>Libellé court de l'organisation</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -648,11 +650,14 @@
     <t>description</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-description}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Organization.description}
 </t>
   </si>
   <si>
-    <t>FR Core Organization Description Extension</t>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -661,11 +666,81 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period}
+    <t xml:space="preserve">Extension {organization-period|5.2.0}
 </t>
   </si>
   <si>
     <t>The date range that this organization should be considered available.</t>
+  </si>
+  <si>
+    <t>Organization.extension:openReason</t>
+  </si>
+  <si>
+    <t>openReason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {note|5.2.0}
+</t>
+  </si>
+  <si>
+    <t>Additional notes that apply to this resource or element.</t>
+  </si>
+  <si>
+    <t>This extension SHALL NOT be used if the resource already has standard 'note' element (or equivalent) of type Annotation on the same element</t>
+  </si>
+  <si>
+    <t>Organization.extension:closureReason</t>
+  </si>
+  <si>
+    <t>closureReason</t>
+  </si>
+  <si>
+    <t>Organization.extension:member</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>FR Core Organization Extension - quelles sont les entités qui font partie de l'organisation</t>
+  </si>
+  <si>
+    <t>Extension permettant de définir des membres d'une organisation. Les membres sont des organisations filles de la ressources. C'est la relation inverse de partOf.</t>
+  </si>
+  <si>
+    <t>Organization.extension:disciplinePrestation</t>
+  </si>
+  <si>
+    <t>disciplinePrestation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-discipline-prestation|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>FR Core Organization Extension - Discipline Prestation</t>
+  </si>
+  <si>
+    <t>Discipline de prestation d'une UAC</t>
+  </si>
+  <si>
+    <t>Organization.extension:tarif</t>
+  </si>
+  <si>
+    <t>tarif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-tarif|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>FR Core Organization Extension - Tarif Soin</t>
+  </si>
+  <si>
+    <t>Tarif de soin associé à l'unité d'activité (UAC, parfois appelé PAC). Le PAC ou l’UAC est le niveau élémentaire de recueil des activités en vue de la facturation. Il est lié à une discipline de prestation et à un tarif (lié à la discipline de prestation). Le PAC ne sert qu’à la facturation du séjour. Il permet d’associer des tarifs de soins différents pour la prise en charge d’un patient.</t>
   </si>
   <si>
     <t>Organization.modifierExtension</t>
@@ -716,213 +791,46 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>Organization.identifier.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
+    <t>Organization.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Whether the organization's record is still in active use</t>
+  </si>
+  <si>
+    <t>Whether the organization's record is still in active use.</t>
+  </si>
+  <si>
+    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
+This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>No equivalent in HL7 v2</t>
+  </si>
+  <si>
+    <t>.status</t>
+  </si>
+  <si>
+    <t>./Status (however this concept in ServD more covers why the organization is active or not, could be delisted, deregistered, not operational yet) this could alternatively be derived from ./StartDate and ./EndDate and given a context date.</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Organization.type</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>./IdentifierType</t>
-  </si>
-  <si>
-    <t>Organization.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>./Value</t>
-  </si>
-  <si>
-    <t>Organization.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>Organization.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>./IdentifierIssuingAuthority</t>
-  </si>
-  <si>
-    <t>Organization.active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Whether the organization's record is still in active use</t>
-  </si>
-  <si>
-    <t>Whether the organization's record is still in active use.</t>
-  </si>
-  <si>
-    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
-This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
-  </si>
-  <si>
-    <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
-  </si>
-  <si>
-    <t>No equivalent in HL7 v2</t>
-  </si>
-  <si>
-    <t>.status</t>
-  </si>
-  <si>
-    <t>./Status (however this concept in ServD more covers why the organization is active or not, could be delisted, deregistered, not operational yet) this could alternatively be derived from ./StartDate and ./EndDate and given a context date.</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Organization.type</t>
   </si>
   <si>
     <t>Kind of organization</t>
@@ -939,7 +847,15 @@
     <t>Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-3307"/&gt;
+    &lt;code value="UAC"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.2.0</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -994,7 +910,7 @@
     <t>Organization.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -1030,7 +946,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
 </t>
   </si>
   <si>
@@ -1066,7 +982,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-uf|2.2.0)
 </t>
   </si>
   <si>
@@ -1219,7 +1135,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>./type</t>
@@ -1286,7 +1202,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1606,20 +1522,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN53"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="36.4609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="36.4609375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.89453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.3515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="31.44921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="83.953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="83.89453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1628,26 +1544,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.5234375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="33.4296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.71875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.65625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="99.8984375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="210.3203125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.58203125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="42.32421875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="181.4296875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2842,7 +2758,7 @@
         <v>78</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>78</v>
@@ -3738,7 +3654,7 @@
         <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3798,7 +3714,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -3818,13 +3734,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -3846,13 +3762,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3912,7 +3828,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -3921,7 +3837,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -3932,13 +3848,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -3960,13 +3876,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4046,46 +3962,46 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>109</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>78</v>
       </c>
@@ -4133,7 +4049,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4151,7 +4067,7 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -4162,12 +4078,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4176,7 +4094,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>78</v>
@@ -4185,21 +4103,21 @@
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>218</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4247,7 +4165,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4256,32 +4174,34 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
       </c>
@@ -4290,7 +4210,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
@@ -4302,13 +4222,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>103</v>
+        <v>221</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>104</v>
+        <v>222</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4359,25 +4279,25 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4388,21 +4308,23 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="D25" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -4414,17 +4336,15 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>109</v>
+        <v>225</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>110</v>
+        <v>226</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4461,19 +4381,19 @@
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>116</v>
+        <v>195</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4491,7 +4411,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4502,12 +4422,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4522,26 +4444,22 @@
         <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4565,11 +4483,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4587,25 +4507,25 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4616,45 +4536,45 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4679,11 +4599,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>241</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -4701,25 +4623,25 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -4730,10 +4652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4741,10 +4663,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -4756,19 +4678,17 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>130</v>
+        <v>239</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4781,7 +4701,7 @@
         <v>78</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>78</v>
@@ -4817,39 +4737,39 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>78</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4857,7 +4777,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -4866,28 +4786,32 @@
         <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>102</v>
+        <v>249</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q29" s="2"/>
+      <c r="Q29" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="R29" t="s" s="2">
         <v>78</v>
       </c>
@@ -4895,7 +4819,7 @@
         <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>78</v>
@@ -4931,7 +4855,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4946,24 +4870,24 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4974,7 +4898,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -4986,22 +4910,26 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>78</v>
@@ -5019,13 +4947,11 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5043,13 +4969,13 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>78</v>
@@ -5058,24 +4984,24 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5098,18 +5024,20 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N31" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5157,7 +5085,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5166,19 +5094,19 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5186,10 +5114,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5200,38 +5128,36 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q32" t="s" s="2">
-        <v>286</v>
-      </c>
+      <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5275,13 +5201,13 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
@@ -5290,24 +5216,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>290</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5327,22 +5253,22 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5367,11 +5293,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5389,7 +5317,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5398,30 +5326,30 @@
         <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>299</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5432,7 +5360,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
@@ -5441,22 +5369,22 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>102</v>
+        <v>295</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5505,28 +5433,28 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI34" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>219</v>
-      </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5534,10 +5462,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5548,7 +5476,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
@@ -5557,22 +5485,20 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>306</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5621,13 +5547,13 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
@@ -5636,13 +5562,13 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>255</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5650,10 +5576,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5664,7 +5590,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -5676,20 +5602,16 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>314</v>
+        <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>315</v>
+        <v>103</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5737,28 +5659,28 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>105</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>319</v>
+        <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>320</v>
+        <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>322</v>
+        <v>106</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>323</v>
+        <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5766,14 +5688,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5792,20 +5714,18 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>325</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>326</v>
+        <v>110</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -5841,19 +5761,19 @@
         <v>78</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>116</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5862,19 +5782,19 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>330</v>
+        <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>331</v>
+        <v>117</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>333</v>
+        <v>106</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5882,10 +5802,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5908,18 +5828,18 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>336</v>
+        <v>102</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
       </c>
@@ -5967,7 +5887,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5976,19 +5896,19 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>318</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>340</v>
+        <v>191</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -5996,10 +5916,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6019,18 +5939,20 @@
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6055,13 +5977,11 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -6079,7 +5999,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>105</v>
+        <v>323</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6091,13 +6011,13 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6108,21 +6028,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -6131,19 +6051,19 @@
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>109</v>
+        <v>239</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>110</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>111</v>
+        <v>326</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>112</v>
+        <v>327</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6181,37 +6101,37 @@
         <v>78</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>116</v>
+        <v>328</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>106</v>
+        <v>329</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6222,10 +6142,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6251,13 +6171,13 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6307,7 +6227,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6316,7 +6236,7 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>100</v>
@@ -6336,10 +6256,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6350,7 +6270,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -6359,21 +6279,23 @@
         <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>130</v>
+        <v>336</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6397,11 +6319,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6419,13 +6343,13 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>78</v>
@@ -6437,7 +6361,7 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>191</v>
+        <v>341</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6448,10 +6372,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6471,20 +6395,18 @@
         <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>215</v>
+        <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>355</v>
+        <v>103</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6533,7 +6455,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6545,13 +6467,13 @@
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>359</v>
+        <v>106</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6562,21 +6484,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -6585,19 +6507,19 @@
         <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>361</v>
+        <v>110</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>362</v>
+        <v>111</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>363</v>
+        <v>112</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6647,25 +6569,25 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>116</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -6676,14 +6598,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6696,25 +6618,25 @@
         <v>78</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>366</v>
+        <v>109</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>369</v>
+        <v>112</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>370</v>
+        <v>236</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6763,7 +6685,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6775,13 +6697,13 @@
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>371</v>
+        <v>191</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -6792,10 +6714,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6818,16 +6740,18 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>102</v>
+        <v>260</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>103</v>
+        <v>350</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>104</v>
+        <v>351</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -6851,13 +6775,13 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>78</v>
+        <v>353</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>78</v>
+        <v>354</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -6875,7 +6799,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>105</v>
+        <v>349</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6887,13 +6811,13 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -6904,21 +6828,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -6930,18 +6854,18 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>109</v>
+        <v>357</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>110</v>
+        <v>358</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -6989,25 +6913,25 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>116</v>
+        <v>356</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>78</v>
+        <v>361</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>106</v>
+        <v>362</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7018,14 +6942,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7038,25 +6962,23 @@
         <v>78</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>109</v>
+        <v>284</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>212</v>
+        <v>366</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7105,7 +7027,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7117,13 +7039,13 @@
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>78</v>
+        <v>367</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>191</v>
+        <v>368</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7134,10 +7056,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7160,17 +7082,17 @@
         <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7195,13 +7117,13 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7219,7 +7141,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7234,10 +7156,10 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>78</v>
+        <v>373</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7248,10 +7170,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7262,7 +7184,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>78</v>
@@ -7274,17 +7196,17 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7333,13 +7255,13 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>78</v>
@@ -7348,357 +7270,15 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>392</v>
+        <v>106</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN53" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-organization-uac.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="410">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ce profil permet de représenter les unités d'activité (UAC, parfois appelé PAC). L'UAC (Unité d'Activité) est le niveau élémentaire de recueil des activités en vue de la facturation.</t>
+    <t>This profile specializes the fr-core-organization profile to represent administrative units inside healthcare institutions.
+Ce profil spécialise le profil fr-core-organization pour représenter les unités administratives et comptables (UAC) en établissement</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Organization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -423,7 +424,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -436,14 +437,14 @@
     <t>Organization.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -487,7 +488,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -511,7 +512,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -554,7 +555,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -630,14 +631,11 @@
     <t>shortName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name}
 </t>
   </si>
   <si>
     <t>FR Core Organization Short Name Extension</t>
-  </si>
-  <si>
-    <t>Libellé court de l'organisation</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -650,14 +648,11 @@
     <t>description</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Organization.description}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-description}
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>FR Core Organization Description Extension</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -666,81 +661,11 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period|5.2.0}
+    <t xml:space="preserve">Extension {organization-period}
 </t>
   </si>
   <si>
     <t>The date range that this organization should be considered available.</t>
-  </si>
-  <si>
-    <t>Organization.extension:openReason</t>
-  </si>
-  <si>
-    <t>openReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {note|5.2.0}
-</t>
-  </si>
-  <si>
-    <t>Additional notes that apply to this resource or element.</t>
-  </si>
-  <si>
-    <t>This extension SHALL NOT be used if the resource already has standard 'note' element (or equivalent) of type Annotation on the same element</t>
-  </si>
-  <si>
-    <t>Organization.extension:closureReason</t>
-  </si>
-  <si>
-    <t>closureReason</t>
-  </si>
-  <si>
-    <t>Organization.extension:member</t>
-  </si>
-  <si>
-    <t>member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0}
-</t>
-  </si>
-  <si>
-    <t>FR Core Organization Extension - quelles sont les entités qui font partie de l'organisation</t>
-  </si>
-  <si>
-    <t>Extension permettant de définir des membres d'une organisation. Les membres sont des organisations filles de la ressources. C'est la relation inverse de partOf.</t>
-  </si>
-  <si>
-    <t>Organization.extension:disciplinePrestation</t>
-  </si>
-  <si>
-    <t>disciplinePrestation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-discipline-prestation|2.2.0}
-</t>
-  </si>
-  <si>
-    <t>FR Core Organization Extension - Discipline Prestation</t>
-  </si>
-  <si>
-    <t>Discipline de prestation d'une UAC</t>
-  </si>
-  <si>
-    <t>Organization.extension:tarif</t>
-  </si>
-  <si>
-    <t>tarif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-tarif|2.2.0}
-</t>
-  </si>
-  <si>
-    <t>FR Core Organization Extension - Tarif Soin</t>
-  </si>
-  <si>
-    <t>Tarif de soin associé à l'unité d'activité (UAC, parfois appelé PAC). Le PAC ou l’UAC est le niveau élémentaire de recueil des activités en vue de la facturation. Il est lié à une discipline de prestation et à un tarif (lié à la discipline de prestation). Le PAC ne sert qu’à la facturation du séjour. Il permet d’associer des tarifs de soins différents pour la prise en charge d’un patient.</t>
   </si>
   <si>
     <t>Organization.modifierExtension</t>
@@ -791,6 +716,177 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>Organization.identifier.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Organization.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>./IdentifierType</t>
+  </si>
+  <si>
+    <t>Organization.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>./Value</t>
+  </si>
+  <si>
+    <t>Organization.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>./StartDate and ./EndDate</t>
+  </si>
+  <si>
+    <t>Organization.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>./IdentifierIssuingAuthority</t>
+  </si>
+  <si>
     <t>Organization.active</t>
   </si>
   <si>
@@ -827,10 +923,6 @@
   </si>
   <si>
     <t>Organization.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Kind of organization</t>
@@ -847,15 +939,7 @@
     <t>Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-3307"/&gt;
-    &lt;code value="UAC"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -910,7 +994,7 @@
     <t>Organization.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
+    <t xml:space="preserve">ContactPoint
 </t>
   </si>
   <si>
@@ -946,7 +1030,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
+    <t xml:space="preserve">Address
 </t>
   </si>
   <si>
@@ -982,7 +1066,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-uf|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -1135,7 +1219,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
   </si>
   <si>
     <t>./type</t>
@@ -1202,7 +1286,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint|4.0.1)
+    <t xml:space="preserve">Reference(Endpoint)
 </t>
   </si>
   <si>
@@ -1522,20 +1606,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.3515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="31.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.4609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.4609375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.89453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="83.89453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="83.953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1544,26 +1628,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.71875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.5234375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="33.4296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.58203125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="42.32421875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="181.4296875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="29.65625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="99.8984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="210.3203125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="33.05078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2758,7 +2842,7 @@
         <v>78</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>78</v>
@@ -3654,7 +3738,7 @@
         <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3714,7 +3798,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -3734,13 +3818,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -3762,13 +3846,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>205</v>
-      </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3828,7 +3912,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -3837,7 +3921,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -3848,13 +3932,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -3876,13 +3960,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3962,46 +4046,46 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
       </c>
@@ -4049,7 +4133,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4067,7 +4151,7 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -4078,14 +4162,12 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4094,7 +4176,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>78</v>
@@ -4103,21 +4185,21 @@
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4165,7 +4247,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4174,34 +4256,32 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>78</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>78</v>
       </c>
@@ -4210,7 +4290,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
@@ -4222,13 +4302,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
+        <v>104</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4279,25 +4359,25 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4308,23 +4388,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -4336,15 +4414,17 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>225</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>110</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4381,19 +4461,19 @@
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>195</v>
+        <v>116</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4411,7 +4491,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4422,14 +4502,12 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4444,22 +4522,26 @@
         <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4483,13 +4565,11 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4507,25 +4587,25 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4536,45 +4616,45 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J27" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>109</v>
+        <v>236</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4599,13 +4679,11 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -4623,25 +4701,25 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -4652,10 +4730,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4663,10 +4741,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -4678,17 +4756,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>239</v>
+        <v>130</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4701,7 +4781,7 @@
         <v>78</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>78</v>
@@ -4737,39 +4817,39 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4777,7 +4857,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -4786,32 +4866,28 @@
         <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>249</v>
+        <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q29" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
         <v>78</v>
       </c>
@@ -4819,7 +4895,7 @@
         <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>78</v>
@@ -4855,7 +4931,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4870,24 +4946,24 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4898,7 +4974,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -4910,26 +4986,22 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>265</v>
+        <v>78</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>78</v>
@@ -4947,11 +5019,13 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>266</v>
+        <v>78</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -4969,13 +5043,13 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>78</v>
@@ -4984,24 +5058,24 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>269</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5024,20 +5098,18 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>102</v>
+        <v>272</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5085,7 +5157,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5094,19 +5166,19 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5114,10 +5186,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5128,86 +5200,88 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>102</v>
+        <v>281</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="R32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N32" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="P32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
@@ -5216,24 +5290,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>78</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5253,22 +5327,22 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5293,13 +5367,11 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5317,7 +5389,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5326,30 +5398,30 @@
         <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>290</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>78</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5360,7 +5432,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
@@ -5369,22 +5441,22 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>295</v>
+        <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5433,28 +5505,28 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>300</v>
+        <v>219</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>301</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5462,10 +5534,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5476,7 +5548,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
@@ -5485,20 +5557,22 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>306</v>
+        <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5547,13 +5621,13 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
@@ -5562,13 +5636,13 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5576,10 +5650,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5590,7 +5664,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -5602,16 +5676,20 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>102</v>
+        <v>314</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>103</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5659,28 +5737,28 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>105</v>
+        <v>313</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>319</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>78</v>
+        <v>320</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>78</v>
+        <v>321</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>106</v>
+        <v>322</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>78</v>
+        <v>323</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5688,14 +5766,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5714,18 +5792,20 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>325</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>110</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -5761,19 +5841,19 @@
         <v>78</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>116</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5782,19 +5862,19 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>117</v>
+        <v>331</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>78</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5802,10 +5882,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5828,18 +5908,18 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>102</v>
+        <v>336</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
       </c>
@@ -5887,7 +5967,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5896,19 +5976,19 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>318</v>
+        <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>191</v>
+        <v>340</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -5916,10 +5996,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5939,20 +6019,18 @@
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>103</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -5977,11 +6055,13 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>266</v>
+        <v>78</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -5999,7 +6079,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>323</v>
+        <v>105</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6011,13 +6091,13 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6028,21 +6108,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -6051,19 +6131,19 @@
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>239</v>
+        <v>109</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>325</v>
+        <v>110</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>326</v>
+        <v>111</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>327</v>
+        <v>112</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6101,37 +6181,37 @@
         <v>78</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>328</v>
+        <v>116</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>329</v>
+        <v>106</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6142,10 +6222,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6171,13 +6251,13 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6227,7 +6307,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6236,7 +6316,7 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>100</v>
@@ -6256,10 +6336,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6270,7 +6350,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -6279,23 +6359,21 @@
         <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>336</v>
+        <v>130</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6319,13 +6397,11 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6343,13 +6419,13 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>78</v>
@@ -6361,7 +6437,7 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>341</v>
+        <v>191</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6372,10 +6448,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6395,18 +6471,20 @@
         <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>103</v>
+        <v>355</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6455,7 +6533,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>105</v>
+        <v>358</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6467,13 +6545,13 @@
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>106</v>
+        <v>359</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6484,21 +6562,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -6507,19 +6585,19 @@
         <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>110</v>
+        <v>361</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>111</v>
+        <v>362</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>112</v>
+        <v>363</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6569,25 +6647,25 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>116</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -6598,14 +6676,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6618,25 +6696,25 @@
         <v>78</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>109</v>
+        <v>366</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>112</v>
+        <v>369</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>236</v>
+        <v>370</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6685,7 +6763,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6697,13 +6775,13 @@
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -6714,10 +6792,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6740,18 +6818,16 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>260</v>
+        <v>102</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>350</v>
+        <v>103</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>351</v>
+        <v>104</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>352</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -6775,13 +6851,13 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>353</v>
+        <v>78</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>354</v>
+        <v>78</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -6799,7 +6875,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>349</v>
+        <v>105</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6811,13 +6887,13 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>355</v>
+        <v>106</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -6828,21 +6904,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -6854,18 +6930,18 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>357</v>
+        <v>109</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>358</v>
+        <v>110</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -6913,25 +6989,25 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>356</v>
+        <v>116</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>361</v>
+        <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>362</v>
+        <v>106</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -6942,14 +7018,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>78</v>
+        <v>375</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6962,23 +7038,25 @@
         <v>78</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>284</v>
+        <v>109</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>366</v>
+        <v>212</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7027,7 +7105,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7039,13 +7117,13 @@
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>367</v>
+        <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>368</v>
+        <v>191</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7056,10 +7134,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7082,17 +7160,17 @@
         <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>295</v>
+        <v>236</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7117,13 +7195,13 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>78</v>
+        <v>384</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7141,7 +7219,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7156,10 +7234,10 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>373</v>
+        <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7170,10 +7248,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7184,7 +7262,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>78</v>
@@ -7196,17 +7274,17 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7255,13 +7333,13 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>78</v>
@@ -7270,15 +7348,357 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AM53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-organization-uac.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="380">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,8 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This profile specializes the fr-core-organization profile to represent administrative units inside healthcare institutions.
-Ce profil spécialise le profil fr-core-organization pour représenter les unités administratives et comptables (UAC) en établissement</t>
+    <t>Ce profil permet de représenter les unités d'activité (UAC, parfois appelé PAC). L'UAC (Unité d'Activité) est le niveau élémentaire de recueil des activités en vue de la facturation.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -115,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Organization</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -424,7 +423,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -437,14 +436,14 @@
     <t>Organization.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -488,7 +487,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -512,7 +511,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -555,7 +554,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -631,11 +630,14 @@
     <t>shortName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Organization Short Name Extension</t>
+  </si>
+  <si>
+    <t>Libellé court de l'organisation</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -648,11 +650,14 @@
     <t>description</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-description}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Organization.description}
 </t>
   </si>
   <si>
-    <t>FR Core Organization Description Extension</t>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -661,11 +666,81 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period}
+    <t xml:space="preserve">Extension {organization-period|5.2.0}
 </t>
   </si>
   <si>
     <t>The date range that this organization should be considered available.</t>
+  </si>
+  <si>
+    <t>Organization.extension:openReason</t>
+  </si>
+  <si>
+    <t>openReason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {note|5.2.0}
+</t>
+  </si>
+  <si>
+    <t>Additional notes that apply to this resource or element.</t>
+  </si>
+  <si>
+    <t>This extension SHALL NOT be used if the resource already has standard 'note' element (or equivalent) of type Annotation on the same element</t>
+  </si>
+  <si>
+    <t>Organization.extension:closureReason</t>
+  </si>
+  <si>
+    <t>closureReason</t>
+  </si>
+  <si>
+    <t>Organization.extension:member</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>FR Core Organization Extension - quelles sont les entités qui font partie de l'organisation</t>
+  </si>
+  <si>
+    <t>Extension permettant de définir des membres d'une organisation. Les membres sont des organisations filles de la ressources. C'est la relation inverse de partOf.</t>
+  </si>
+  <si>
+    <t>Organization.extension:disciplinePrestation</t>
+  </si>
+  <si>
+    <t>disciplinePrestation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-discipline-prestation|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>FR Core Organization Extension - Discipline Prestation</t>
+  </si>
+  <si>
+    <t>Discipline de prestation d'une UAC</t>
+  </si>
+  <si>
+    <t>Organization.extension:tarif</t>
+  </si>
+  <si>
+    <t>tarif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-tarif|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>FR Core Organization Extension - Tarif Soin</t>
+  </si>
+  <si>
+    <t>Tarif de soin associé à l'unité d'activité (UAC, parfois appelé PAC). Le PAC ou l’UAC est le niveau élémentaire de recueil des activités en vue de la facturation. Il est lié à une discipline de prestation et à un tarif (lié à la discipline de prestation). Le PAC ne sert qu’à la facturation du séjour. Il permet d’associer des tarifs de soins différents pour la prise en charge d’un patient.</t>
   </si>
   <si>
     <t>Organization.modifierExtension</t>
@@ -716,213 +791,46 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>Organization.identifier.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
+    <t>Organization.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Whether the organization's record is still in active use</t>
+  </si>
+  <si>
+    <t>Whether the organization's record is still in active use.</t>
+  </si>
+  <si>
+    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
+This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>No equivalent in HL7 v2</t>
+  </si>
+  <si>
+    <t>.status</t>
+  </si>
+  <si>
+    <t>./Status (however this concept in ServD more covers why the organization is active or not, could be delisted, deregistered, not operational yet) this could alternatively be derived from ./StartDate and ./EndDate and given a context date.</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Organization.type</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>./IdentifierType</t>
-  </si>
-  <si>
-    <t>Organization.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>./Value</t>
-  </si>
-  <si>
-    <t>Organization.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>Organization.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>./IdentifierIssuingAuthority</t>
-  </si>
-  <si>
-    <t>Organization.active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Whether the organization's record is still in active use</t>
-  </si>
-  <si>
-    <t>Whether the organization's record is still in active use.</t>
-  </si>
-  <si>
-    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
-This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
-  </si>
-  <si>
-    <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
-  </si>
-  <si>
-    <t>No equivalent in HL7 v2</t>
-  </si>
-  <si>
-    <t>.status</t>
-  </si>
-  <si>
-    <t>./Status (however this concept in ServD more covers why the organization is active or not, could be delisted, deregistered, not operational yet) this could alternatively be derived from ./StartDate and ./EndDate and given a context date.</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Organization.type</t>
   </si>
   <si>
     <t>Kind of organization</t>
@@ -939,7 +847,15 @@
     <t>Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-3307"/&gt;
+    &lt;code value="UAC"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.2.0</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -994,7 +910,7 @@
     <t>Organization.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -1030,7 +946,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
 </t>
   </si>
   <si>
@@ -1066,7 +982,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-uf|2.2.0)
 </t>
   </si>
   <si>
@@ -1219,7 +1135,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>./type</t>
@@ -1286,7 +1202,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1606,20 +1522,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN53"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="36.4609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="36.4609375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.89453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.3515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="31.44921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="83.953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="83.89453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1628,26 +1544,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.5234375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="33.4296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.71875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.65625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="99.8984375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="210.3203125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.58203125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="42.32421875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="181.4296875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2842,7 +2758,7 @@
         <v>78</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>78</v>
@@ -3738,7 +3654,7 @@
         <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3798,7 +3714,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -3818,13 +3734,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -3846,13 +3762,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3912,7 +3828,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -3921,7 +3837,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -3932,13 +3848,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -3960,13 +3876,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4046,46 +3962,46 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>109</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>78</v>
       </c>
@@ -4133,7 +4049,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4151,7 +4067,7 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -4162,12 +4078,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4176,7 +4094,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>78</v>
@@ -4185,21 +4103,21 @@
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>218</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4247,7 +4165,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4256,32 +4174,34 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
       </c>
@@ -4290,7 +4210,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
@@ -4302,13 +4222,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>103</v>
+        <v>221</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>104</v>
+        <v>222</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4359,25 +4279,25 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4388,21 +4308,23 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="D25" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -4414,17 +4336,15 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>109</v>
+        <v>225</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>110</v>
+        <v>226</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4461,19 +4381,19 @@
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>116</v>
+        <v>195</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4491,7 +4411,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4502,12 +4422,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4522,26 +4444,22 @@
         <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4565,11 +4483,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4587,25 +4507,25 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4616,45 +4536,45 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4679,11 +4599,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>241</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -4701,25 +4623,25 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -4730,10 +4652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4741,10 +4663,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -4756,19 +4678,17 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>130</v>
+        <v>239</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4781,7 +4701,7 @@
         <v>78</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>78</v>
@@ -4817,39 +4737,39 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>78</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4857,7 +4777,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -4866,28 +4786,32 @@
         <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>102</v>
+        <v>249</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q29" s="2"/>
+      <c r="Q29" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="R29" t="s" s="2">
         <v>78</v>
       </c>
@@ -4895,7 +4819,7 @@
         <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>78</v>
@@ -4931,7 +4855,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4946,24 +4870,24 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4974,7 +4898,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -4986,22 +4910,26 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>78</v>
@@ -5019,13 +4947,11 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5043,13 +4969,13 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>78</v>
@@ -5058,24 +4984,24 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5098,18 +5024,20 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N31" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5157,7 +5085,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5166,19 +5094,19 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5186,10 +5114,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5200,38 +5128,36 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q32" t="s" s="2">
-        <v>286</v>
-      </c>
+      <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5275,13 +5201,13 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
@@ -5290,24 +5216,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>290</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5327,22 +5253,22 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5367,11 +5293,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5389,7 +5317,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5398,30 +5326,30 @@
         <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>299</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5432,7 +5360,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
@@ -5441,22 +5369,22 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>102</v>
+        <v>295</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5505,28 +5433,28 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI34" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>219</v>
-      </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5534,10 +5462,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5548,7 +5476,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
@@ -5557,22 +5485,20 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>306</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5621,13 +5547,13 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
@@ -5636,13 +5562,13 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>255</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5650,10 +5576,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5664,7 +5590,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -5676,20 +5602,16 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>314</v>
+        <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>315</v>
+        <v>103</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5737,28 +5659,28 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>105</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>319</v>
+        <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>320</v>
+        <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>322</v>
+        <v>106</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>323</v>
+        <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5766,14 +5688,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5792,20 +5714,18 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>325</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>326</v>
+        <v>110</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -5841,19 +5761,19 @@
         <v>78</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>116</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5862,19 +5782,19 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>330</v>
+        <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>331</v>
+        <v>117</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>333</v>
+        <v>106</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5882,10 +5802,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5908,18 +5828,18 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>336</v>
+        <v>102</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
       </c>
@@ -5967,7 +5887,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5976,19 +5896,19 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>318</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>340</v>
+        <v>191</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -5996,10 +5916,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6019,18 +5939,20 @@
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6055,13 +5977,11 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -6079,7 +5999,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>105</v>
+        <v>323</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6091,13 +6011,13 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6108,21 +6028,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -6131,19 +6051,19 @@
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>109</v>
+        <v>239</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>110</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>111</v>
+        <v>326</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>112</v>
+        <v>327</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6181,37 +6101,37 @@
         <v>78</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>116</v>
+        <v>328</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>106</v>
+        <v>329</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6222,10 +6142,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6251,13 +6171,13 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6307,7 +6227,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6316,7 +6236,7 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>100</v>
@@ -6336,10 +6256,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6350,7 +6270,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -6359,21 +6279,23 @@
         <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>130</v>
+        <v>336</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6397,11 +6319,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6419,13 +6343,13 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>78</v>
@@ -6437,7 +6361,7 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>191</v>
+        <v>341</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6448,10 +6372,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6471,20 +6395,18 @@
         <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>215</v>
+        <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>355</v>
+        <v>103</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6533,7 +6455,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6545,13 +6467,13 @@
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>359</v>
+        <v>106</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6562,21 +6484,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -6585,19 +6507,19 @@
         <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>361</v>
+        <v>110</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>362</v>
+        <v>111</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>363</v>
+        <v>112</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6647,25 +6569,25 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>116</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -6676,14 +6598,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6696,25 +6618,25 @@
         <v>78</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>366</v>
+        <v>109</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>369</v>
+        <v>112</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>370</v>
+        <v>236</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6763,7 +6685,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6775,13 +6697,13 @@
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>371</v>
+        <v>191</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -6792,10 +6714,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6818,16 +6740,18 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>102</v>
+        <v>260</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>103</v>
+        <v>350</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>104</v>
+        <v>351</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -6851,13 +6775,13 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>78</v>
+        <v>353</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>78</v>
+        <v>354</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -6875,7 +6799,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>105</v>
+        <v>349</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6887,13 +6811,13 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -6904,21 +6828,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -6930,18 +6854,18 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>109</v>
+        <v>357</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>110</v>
+        <v>358</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -6989,25 +6913,25 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>116</v>
+        <v>356</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>78</v>
+        <v>361</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>106</v>
+        <v>362</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7018,14 +6942,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7038,25 +6962,23 @@
         <v>78</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>109</v>
+        <v>284</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>212</v>
+        <v>366</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7105,7 +7027,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7117,13 +7039,13 @@
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>78</v>
+        <v>367</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>191</v>
+        <v>368</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7134,10 +7056,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7160,17 +7082,17 @@
         <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7195,13 +7117,13 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7219,7 +7141,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7234,10 +7156,10 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>78</v>
+        <v>373</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7248,10 +7170,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7262,7 +7184,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>78</v>
@@ -7274,17 +7196,17 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7333,13 +7255,13 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>78</v>
@@ -7348,357 +7270,15 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>392</v>
+        <v>106</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN53" t="s" s="2">
         <v>78</v>
       </c>
     </row>
